--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484225_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484225_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5165</v>
+        <v>2.3365</v>
       </c>
       <c r="E2" t="n">
-        <v>3.601</v>
+        <v>2.4482</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1117</v>
       </c>
       <c r="G2" t="n">
         <v>2.2285</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6092</v>
+        <v>-0.5709</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7556</v>
+        <v>0.6027</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1464</v>
+        <v>-1.1736</v>
       </c>
       <c r="V2" t="n">
         <v>0.2882</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9748</v>
+        <v>1.2472</v>
       </c>
       <c r="E3" t="n">
         <v>0.2089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.766</v>
+        <v>1.0383</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5738</v>
@@ -688,13 +688,13 @@
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.6163</v>
       </c>
       <c r="T3" t="n">
         <v>0.0964</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9851</v>
+        <v>-0.7127</v>
       </c>
       <c r="V3" t="n">
         <v>2.4373</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4664</v>
+        <v>0.7698</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9207</v>
+        <v>1.224</v>
       </c>
       <c r="F4" t="n">
         <v>-0.4543</v>
@@ -766,10 +766,10 @@
         <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4087</v>
+        <v>-1.1054</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7125</v>
+        <v>-0.4092</v>
       </c>
       <c r="U4" t="n">
         <v>-0.6962</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2852</v>
+        <v>0.7658</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0644</v>
+        <v>0.3272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2208</v>
+        <v>0.4386</v>
       </c>
       <c r="G5" t="n">
         <v>1.7524</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5248</v>
+        <v>-1.0441</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.1914</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4534</v>
+        <v>-1.2355</v>
       </c>
       <c r="V5" t="n">
         <v>1.2296</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5333</v>
+        <v>-0.2162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.524</v>
+        <v>-0.4702</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0573</v>
+        <v>0.254</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1557</v>
+        <v>-0.8226</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6705</v>
+        <v>-1.766</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4852</v>
+        <v>0.9433</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1055</v>
+        <v>-0.9977</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0246</v>
+        <v>-0.9977</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0502</v>
+        <v>0.1751</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.354</v>
+        <v>-0.7682</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4043</v>
+        <v>0.9433</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8617</v>
+        <v>-0.5303</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0594</v>
+        <v>0.2856</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1976</v>
+        <v>-0.8159</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.16</v>
+        <v>0.9414</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.755</v>
+        <v>-0.7329</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0363</v>
+        <v>0.2444</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2813</v>
+        <v>-0.9774</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8226</v>
+        <v>0.4561</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.766</v>
+        <v>-0.218</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9433</v>
+        <v>0.6741</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9977</v>
+        <v>0.0614</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9977</v>
+        <v>0.0614</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1751</v>
+        <v>0.3948</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7682</v>
+        <v>-0.2793</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9433</v>
+        <v>0.6741</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0692</v>
+        <v>-0.2792</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2805</v>
+        <v>0.183</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7887</v>
+        <v>-0.4623</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9414</v>
+        <v>-1.4959</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3941</v>
+        <v>-1.3228</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3623</v>
+        <v>-0.1838</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0318</v>
+        <v>-1.139</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4561</v>
+        <v>1.1557</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.218</v>
+        <v>0.6705</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6741</v>
+        <v>0.4852</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0614</v>
+        <v>1.1055</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0614</v>
+        <v>1.0246</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3948</v>
+        <v>0.0502</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2793</v>
+        <v>-0.354</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6741</v>
+        <v>0.4043</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9404</v>
+        <v>0.0722</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4237</v>
+        <v>0.3516</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5167</v>
+        <v>-0.2793</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>-2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
         <v>-1.4959</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2583</v>
+        <v>-3.2213</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.004</v>
+        <v>-3.8591</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2543</v>
+        <v>0.6378</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4646</v>
+        <v>-3.1051</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0747</v>
+        <v>-1.8913</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5393</v>
+        <v>-1.2138</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-3.1454</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-1.1231</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2.0223</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4646</v>
+        <v>0.0403</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0747</v>
+        <v>-0.7682</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5393</v>
+        <v>0.8085</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8976</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3631</v>
+        <v>-0.1863</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5003</v>
+        <v>-0.7114</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0169</v>
+        <v>-3.34</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6274</v>
+        <v>-2.004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6105</v>
+        <v>-1.336</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1051</v>
+        <v>0.4646</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8913</v>
+        <v>-0.0747</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2138</v>
+        <v>0.5393</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.1454</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1231</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0223</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0403</v>
+        <v>0.4646</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7682</v>
+        <v>-0.0747</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8085</v>
+        <v>0.5393</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6932</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9546</v>
+        <v>-0.3631</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7386</v>
+        <v>-0.582</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3321</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9481</v>
+        <v>-5.3704</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.406</v>
+        <v>-3.6377</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.542</v>
+        <v>-1.7327</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5931</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.284</v>
+        <v>0.2936</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4099</v>
+        <v>0.3584</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1258</v>
+        <v>-0.0648</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4849</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9107</v>
+        <v>-8.186400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0175</v>
+        <v>-6.1298</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8932</v>
+        <v>-2.0566</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7189</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5981</v>
+        <v>-0.6775</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3374</v>
+        <v>0.2251</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7392</v>
+        <v>-0.9026</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8132</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.5735</v>
+        <v>-17.2707</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.1345</v>
+        <v>-11.8319</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.438800000000001</v>
+        <v>-5.439</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7237</v>
@@ -1438,13 +1438,13 @@
         <v>-2.046799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6770999999999998</v>
+        <v>-0.6771000000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8008</v>
+        <v>-2.800800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.590000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="L13" t="n">
         <v>-5.3908</v>
@@ -1453,10 +1453,10 @@
         <v>0.07719999999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6364</v>
+        <v>-4.636399999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>4.713699999999999</v>
+        <v>4.7137</v>
       </c>
       <c r="P13" t="n">
         <v>-2.9302</v>
@@ -1465,16 +1465,16 @@
         <v>-12.6973</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767099999999999</v>
+        <v>9.767100000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.6033</v>
+        <v>-6.3006</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0331</v>
+        <v>1.3356</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.6364</v>
+        <v>-7.636299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-5.3163</v>
@@ -1483,13 +1483,13 @@
         <v>2.3305</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.646800000000001</v>
+        <v>-7.646799999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9422</v>
+        <v>6.1307</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5148</v>
+        <v>3.4151</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4274</v>
+        <v>2.7155</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6212</v>
+        <v>-0.6152</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1781</v>
+        <v>0.8005</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4431</v>
+        <v>-1.4157</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5159</v>
+        <v>-1.3851</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2072</v>
+        <v>1.109</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3087</v>
+        <v>-2.4941</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1053</v>
+        <v>0.7699</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0291</v>
+        <v>-0.3085</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1344</v>
+        <v>1.0784</v>
       </c>
       <c r="P14" t="n">
         <v>1.1721</v>
@@ -1546,28 +1546,28 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8717</v>
+        <v>1.4183</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2025</v>
+        <v>1.3442</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6692</v>
+        <v>0.0741</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>4.1555</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7731</v>
+        <v>4.4327</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6816</v>
+        <v>5.0853</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2595</v>
+        <v>2.1946</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4221</v>
+        <v>2.8907</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0524</v>
+        <v>2.7724</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5112</v>
+        <v>1.5048</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4587</v>
+        <v>1.2677</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0674</v>
+        <v>1.6531</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6605</v>
+        <v>1.5989</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0543</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.015</v>
+        <v>1.1193</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1494</v>
+        <v>-0.0941</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>1.2134</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3008</v>
+        <v>0.2813</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.5415</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4093</v>
+        <v>-0.2601</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3283</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.0511</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5775</v>
+        <v>4.9628</v>
       </c>
       <c r="E16" t="n">
-        <v>2.404</v>
+        <v>2.4617</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1735</v>
+        <v>2.5011</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6152</v>
+        <v>2.0524</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8005</v>
+        <v>2.5112</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4157</v>
+        <v>-0.4587</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3851</v>
+        <v>2.0674</v>
       </c>
       <c r="K16" t="n">
-        <v>1.109</v>
+        <v>2.6605</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.4941</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7699</v>
+        <v>-0.015</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3085</v>
+        <v>-0.1494</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0784</v>
+        <v>0.1344</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1348</v>
+        <v>1.582</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3331</v>
+        <v>1.0938</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4679</v>
+        <v>0.4883</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1555</v>
+        <v>1.3283</v>
       </c>
       <c r="W16" t="n">
-        <v>4.4327</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>1.0511</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4953</v>
+        <v>4.9359</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0935</v>
+        <v>3.1104</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4018</v>
+        <v>1.8255</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7724</v>
+        <v>1.6212</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5048</v>
+        <v>0.1781</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2677</v>
+        <v>1.4431</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6531</v>
+        <v>1.5159</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5989</v>
+        <v>0.2072</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0543</v>
+        <v>1.3087</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1193</v>
+        <v>0.1053</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0941</v>
+        <v>-0.0291</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2134</v>
+        <v>0.1344</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3087</v>
+        <v>1.8654</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4404</v>
+        <v>0.7981</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.749</v>
+        <v>1.0673</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.132</v>
+        <v>1.482</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9807</v>
+        <v>-0.5762</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1126</v>
+        <v>2.0582</v>
       </c>
       <c r="G18" t="n">
         <v>0.7584</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2125</v>
+        <v>0.1375</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3356</v>
+        <v>0.0689</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1231</v>
+        <v>0.0687</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.08</v>
+        <v>0.2309</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2183</v>
+        <v>-0.7929</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8617</v>
+        <v>1.0238</v>
       </c>
       <c r="G19" t="n">
         <v>1.6764</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7943</v>
+        <v>1.9452</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8533</v>
+        <v>1.8422</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0591</v>
+        <v>0.103</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8279</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0672</v>
+        <v>0.1198</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6289</v>
+        <v>-0.8062</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6962</v>
+        <v>0.926</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4267</v>
+        <v>-1.4953</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.276</v>
+        <v>-1.6854</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8494</v>
+        <v>0.1901</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6119</v>
+        <v>-1.0712</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6524</v>
+        <v>-0.857</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-0.2142</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1852</v>
+        <v>-0.4241</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6237</v>
+        <v>-0.8283</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8089</v>
+        <v>0.4043</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0604</v>
+        <v>0.1342</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6592</v>
+        <v>0.2649</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5988</v>
+        <v>-0.1308</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9962</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.719</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6983</v>
+        <v>-0.416</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1096</v>
+        <v>-0.1739</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4113</v>
+        <v>-0.2422</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4953</v>
+        <v>-1.3277</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6854</v>
+        <v>-2.2989</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1901</v>
+        <v>0.9712</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0712</v>
+        <v>-0.5544</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.857</v>
+        <v>-1.2562</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2142</v>
+        <v>0.7017</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4241</v>
+        <v>-0.7733</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8283</v>
+        <v>-1.0427</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4043</v>
+        <v>0.2694</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6839</v>
+        <v>1.3489</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0384</v>
+        <v>1.3573</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6455</v>
+        <v>-0.0083</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>M. LLUCIÀ MONSÓ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2069</v>
+        <v>-0.926</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4772</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7297</v>
+        <v>-0.2733</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3277</v>
+        <v>-0.968</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2989</v>
+        <v>-0.2937</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9712</v>
+        <v>-0.6743</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5544</v>
+        <v>-0.6933</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2562</v>
+        <v>-0.0192</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7017</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7733</v>
+        <v>-0.2747</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0427</v>
+        <v>-0.2745</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2694</v>
+        <v>-0.0002</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5581</v>
+        <v>0.0419</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0539</v>
+        <v>0.0406</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4959</v>
+        <v>0.0014</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2437</v>
+        <v>-0.9374</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7538</v>
+        <v>-1.7412</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4899</v>
+        <v>0.8038</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.968</v>
+        <v>-0.4267</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2937</v>
+        <v>-1.276</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6743</v>
+        <v>0.8494</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6933</v>
+        <v>-0.6119</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0192</v>
+        <v>-0.6524</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2747</v>
+        <v>0.1852</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2745</v>
+        <v>-0.6237</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0002</v>
+        <v>0.8089</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2757</v>
+        <v>0.0557</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0605</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2152</v>
+        <v>-0.4912</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.9962</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2536</v>
+        <v>-1.0721</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.101</v>
+        <v>-0.9999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1525</v>
+        <v>-0.0722</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3243</v>
@@ -2326,13 +2326,13 @@
         <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3665</v>
+        <v>-0.185</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0033</v>
+        <v>0.077</v>
       </c>
       <c r="V24" t="n">
         <v>1.2186</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.5733</v>
+        <v>19.5959</v>
       </c>
       <c r="E25" t="n">
-        <v>5.438900000000001</v>
+        <v>5.4388</v>
       </c>
       <c r="F25" t="n">
-        <v>12.1345</v>
+        <v>14.1569</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7236</v>
+        <v>2.723599999999999</v>
       </c>
       <c r="H25" t="n">
         <v>2.0468</v>
@@ -2377,7 +2377,7 @@
         <v>0.6771000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.07719999999999994</v>
+        <v>-0.07719999999999982</v>
       </c>
       <c r="K25" t="n">
         <v>4.6365</v>
@@ -2398,19 +2398,19 @@
         <v>2.9303</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.766999999999998</v>
+        <v>-9.766999999999999</v>
       </c>
       <c r="R25" t="n">
         <v>12.6973</v>
       </c>
       <c r="S25" t="n">
-        <v>6.6032</v>
+        <v>8.625400000000001</v>
       </c>
       <c r="T25" t="n">
         <v>7.6364</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0331</v>
+        <v>0.9893999999999998</v>
       </c>
       <c r="V25" t="n">
         <v>5.3163</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484225_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484225_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.2663</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,45 +797,50 @@
       </c>
       <c r="X4" t="n">
         <v>0.011</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7658</v>
+        <v>0.4588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3272</v>
+        <v>0.0202</v>
       </c>
       <c r="F5" t="n">
         <v>0.4386</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7524</v>
+        <v>1.4454</v>
       </c>
       <c r="H5" t="n">
-        <v>0.431</v>
+        <v>0.1241</v>
       </c>
       <c r="I5" t="n">
         <v>1.3214</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8473</v>
+        <v>1.5403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.66</v>
+        <v>0.353</v>
       </c>
       <c r="L5" t="n">
         <v>1.1873</v>
@@ -860,864 +880,920 @@
       </c>
       <c r="X5" t="n">
         <v>0.011</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2162</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4702</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8226</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.766</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9977</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9977</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1751</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7682</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5303</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8159</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7329</v>
+        <v>-0.2162</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2444</v>
+        <v>-0.4702</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9774</v>
+        <v>0.254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4561</v>
+        <v>-0.8226</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.218</v>
+        <v>-1.766</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6741</v>
+        <v>0.9433</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0614</v>
+        <v>-0.9977</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>-0.9977</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3948</v>
+        <v>0.1751</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2793</v>
+        <v>-0.7682</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6741</v>
+        <v>0.9433</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2792</v>
+        <v>-0.5303</v>
       </c>
       <c r="T7" t="n">
-        <v>0.183</v>
+        <v>0.2856</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4623</v>
+        <v>-0.8159</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3228</v>
+        <v>-0.7329</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1838</v>
+        <v>0.2444</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.139</v>
+        <v>-0.9774</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1557</v>
+        <v>0.4561</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6705</v>
+        <v>-0.218</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4852</v>
+        <v>0.6741</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1055</v>
+        <v>0.0614</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0246</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0502</v>
+        <v>0.3948</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.354</v>
+        <v>-0.2793</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4043</v>
+        <v>0.6741</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0722</v>
+        <v>-0.2792</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3516</v>
+        <v>0.183</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2793</v>
+        <v>-0.4623</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.16</v>
+        <v>-1.4959</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2213</v>
+        <v>-1.3228</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8591</v>
+        <v>-0.1838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6378</v>
+        <v>-1.139</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1051</v>
+        <v>1.1557</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8913</v>
+        <v>0.6705</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2138</v>
+        <v>0.4852</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1454</v>
+        <v>1.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1231</v>
+        <v>1.0246</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0223</v>
+        <v>0.0809</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0403</v>
+        <v>0.0502</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7682</v>
+        <v>-0.354</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8085</v>
+        <v>0.4043</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8976</v>
+        <v>0.0722</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1863</v>
+        <v>0.3516</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7114</v>
+        <v>-0.2793</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3321</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.34</v>
+        <v>-3.2213</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.004</v>
+        <v>-3.8591</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.336</v>
+        <v>0.6378</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4646</v>
+        <v>-3.1051</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0747</v>
+        <v>-1.8913</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5393</v>
+        <v>-1.2138</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-3.1454</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-1.1231</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.0223</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4646</v>
+        <v>0.0403</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0747</v>
+        <v>-0.7682</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5393</v>
+        <v>0.8085</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.8976</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3631</v>
+        <v>-0.1863</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.582</v>
+        <v>-0.7114</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3704</v>
+        <v>-3.34</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6377</v>
+        <v>-2.004</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7327</v>
+        <v>-1.336</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5931</v>
+        <v>0.4646</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.813</v>
+        <v>-0.0747</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7801</v>
+        <v>0.5393</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8241</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4493</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3748</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.769</v>
+        <v>0.4646</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3638</v>
+        <v>-0.0747</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4052</v>
+        <v>0.5393</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2936</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3584</v>
+        <v>-0.3631</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0648</v>
+        <v>-0.582</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4849</v>
+        <v>-1.8828</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4849</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.186400000000001</v>
+        <v>-5.3704</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1298</v>
+        <v>-3.6377</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0566</v>
+        <v>-1.7327</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7189</v>
+        <v>-3.5931</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.451</v>
+        <v>-1.813</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2679</v>
+        <v>-1.7801</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8191</v>
+        <v>-2.8241</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8778</v>
+        <v>-1.4493</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9414</v>
+        <v>-1.3748</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1002</v>
+        <v>-0.769</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5733</v>
+        <v>-0.3638</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6735</v>
+        <v>-0.4052</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6775</v>
+        <v>0.2936</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2251</v>
+        <v>0.3584</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9026</v>
+        <v>-0.0648</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8132</v>
+        <v>-1.4849</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4263</v>
+        <v>-1.4849</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.2707</v>
+        <v>-8.186400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.8319</v>
+        <v>-6.1298</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.439</v>
+        <v>-2.0566</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7237</v>
+        <v>-3.7189</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.046799999999999</v>
+        <v>-2.451</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6771000000000003</v>
+        <v>-1.2679</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.800800000000001</v>
+        <v>-3.8191</v>
       </c>
       <c r="K13" t="n">
-        <v>2.59</v>
+        <v>-1.8778</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.3908</v>
+        <v>-1.9414</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07719999999999998</v>
+        <v>0.1002</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.636399999999999</v>
+        <v>-0.5733</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7137</v>
+        <v>0.6735</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9302</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6973</v>
+        <v>-2.1488</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767100000000001</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.3006</v>
+        <v>-0.6775</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3356</v>
+        <v>0.2251</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.636299999999999</v>
+        <v>-0.9026</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.3163</v>
+        <v>-2.8132</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3305</v>
+        <v>-0.3869</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.646799999999999</v>
+        <v>-2.4263</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1307</v>
+        <v>-17.2707</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4151</v>
+        <v>-11.8319</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7155</v>
+        <v>-5.439</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6152</v>
+        <v>-2.723700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8005</v>
+        <v>-2.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4157</v>
+        <v>-0.6771000000000003</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3851</v>
+        <v>-2.800800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.109</v>
+        <v>2.59</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.4941</v>
+        <v>-5.3908</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7699</v>
+        <v>0.07719999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3085</v>
+        <v>-4.6364</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0784</v>
+        <v>4.7137</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>-2.9302</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-12.6973</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>9.767100000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4183</v>
+        <v>-6.3006</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3442</v>
+        <v>1.3356</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0741</v>
+        <v>-7.6363</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1555</v>
+        <v>-5.3163</v>
       </c>
       <c r="W14" t="n">
-        <v>4.4327</v>
+        <v>2.3305</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-7.646799999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0853</v>
+        <v>5.2097</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1946</v>
+        <v>2.4942</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8907</v>
+        <v>2.7155</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7724</v>
+        <v>-1.5362</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5048</v>
+        <v>-0.1205</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2677</v>
+        <v>-1.4157</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6531</v>
+        <v>-2.3061</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5989</v>
+        <v>0.188</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0543</v>
+        <v>-2.4941</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1193</v>
+        <v>0.7699</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0941</v>
+        <v>-0.3085</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2134</v>
+        <v>1.0784</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2813</v>
+        <v>1.4183</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5415</v>
+        <v>1.3442</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2601</v>
+        <v>0.0741</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>4.1555</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.4327</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9628</v>
+        <v>5.0853</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4617</v>
+        <v>2.1946</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5011</v>
+        <v>2.8907</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0524</v>
+        <v>2.7724</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5112</v>
+        <v>1.5048</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4587</v>
+        <v>1.2677</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0674</v>
+        <v>1.6531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6605</v>
+        <v>1.5989</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0543</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.015</v>
+        <v>1.1193</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1494</v>
+        <v>-0.0941</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1344</v>
+        <v>1.2134</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>1.582</v>
+        <v>0.2813</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0938</v>
+        <v>0.5415</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4883</v>
+        <v>-0.2601</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3283</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.0511</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1728,7 +1804,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1796,369 +1872,394 @@
       </c>
       <c r="X17" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.482</v>
+        <v>4.0418</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5762</v>
+        <v>1.5407</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0582</v>
+        <v>2.5011</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7584</v>
+        <v>1.1315</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8522</v>
+        <v>1.5902</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.4587</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6451</v>
+        <v>1.1464</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1228</v>
+        <v>1.7396</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7679</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4035</v>
+        <v>-0.015</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7294</v>
+        <v>-0.1494</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6741</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1375</v>
+        <v>1.582</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0689</v>
+        <v>1.0938</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0687</v>
+        <v>0.4883</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.0511</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2309</v>
+        <v>1.482</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7929</v>
+        <v>-0.5762</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0238</v>
+        <v>2.0582</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6764</v>
+        <v>0.7584</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2692</v>
+        <v>0.8522</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5928</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6272</v>
+        <v>-0.6451</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0286</v>
+        <v>0.1228</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4015</v>
+        <v>-0.7679</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0492</v>
+        <v>1.4035</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2405</v>
+        <v>0.7294</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8087</v>
+        <v>0.6741</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9452</v>
+        <v>0.1375</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8422</v>
+        <v>0.0689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.103</v>
+        <v>0.0687</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1198</v>
+        <v>1.214</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8062</v>
+        <v>1.214</v>
       </c>
       <c r="F20" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4953</v>
+        <v>1.214</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6854</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1901</v>
+        <v>1.214</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0712</v>
+        <v>1.214</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.857</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2142</v>
+        <v>1.214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4241</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8283</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2649</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1308</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.416</v>
+        <v>0.921</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1739</v>
+        <v>0.921</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2422</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3277</v>
+        <v>0.921</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2989</v>
+        <v>0.921</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9712</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5544</v>
+        <v>0.921</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2562</v>
+        <v>0.921</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7017</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7733</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0427</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3489</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3573</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.926</v>
+        <v>0.921</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6526999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2733</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.968</v>
+        <v>0.921</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2937</v>
+        <v>0.921</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6743</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6933</v>
+        <v>0.921</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0192</v>
+        <v>0.921</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2747</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2745</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,13 +2271,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0419</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0014</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,241 +2287,589 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9374</v>
+        <v>0.2309</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7412</v>
+        <v>-0.7929</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8038</v>
+        <v>1.0238</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4267</v>
+        <v>1.6764</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.276</v>
+        <v>2.2692</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8494</v>
+        <v>-0.5928</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6119</v>
+        <v>0.6272</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6524</v>
+        <v>2.0286</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>-1.4015</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1852</v>
+        <v>1.0492</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6237</v>
+        <v>0.2405</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8089</v>
+        <v>0.8087</v>
       </c>
       <c r="P23" t="n">
         <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0557</v>
+        <v>1.9452</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5469000000000001</v>
+        <v>1.8422</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4912</v>
+        <v>0.103</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9962</v>
+        <v>-1.8279</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X23" t="n">
-        <v>0.719</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. GARCIA RODRIGUEZ</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0721</v>
+        <v>0.1198</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9999</v>
+        <v>-0.8062</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0722</v>
+        <v>0.926</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3243</v>
+        <v>-1.4953</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5152</v>
+        <v>-1.6854</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8091</v>
+        <v>0.1901</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9798</v>
+        <v>-1.0712</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3057</v>
+        <v>-0.857</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6741</v>
+        <v>-0.2142</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3445</v>
+        <v>-0.4241</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2095</v>
+        <v>-0.8283</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.135</v>
+        <v>0.4043</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.185</v>
+        <v>0.1342</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.262</v>
+        <v>0.2649</v>
       </c>
       <c r="U24" t="n">
-        <v>0.077</v>
+        <v>-0.1308</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-0.926</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.6526999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.2733</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2937</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.6743</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.6933</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2747</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2745</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F. VILAR FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.9374</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.7412</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.4267</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.276</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8494</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.6119</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.6524</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6237</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5469000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4912</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. GARCIA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.0721</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.9999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.0722</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.3243</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.5152</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8091</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.9798</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.3057</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.3445</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.2095</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.185</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.262</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.3878</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.2422</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.5417</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.2989</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.2428</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.7684</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.2562</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.7733</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.0427</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.3489</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.3573</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484225_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>19.5959</v>
       </c>
-      <c r="E25" t="n">
-        <v>5.4388</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="E29" t="n">
+        <v>5.439000000000002</v>
+      </c>
+      <c r="F29" t="n">
         <v>14.1569</v>
       </c>
-      <c r="G25" t="n">
-        <v>2.723599999999999</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G29" t="n">
+        <v>2.723699999999999</v>
+      </c>
+      <c r="H29" t="n">
         <v>2.0468</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.6771000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.07719999999999982</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.6365</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-4.713900000000001</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="I29" t="n">
+        <v>0.6771000000000003</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.07719999999999927</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.6366</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-4.7138</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.8008</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-2.5899</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>5.3908</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>2.9303</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-9.766999999999999</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>8.625400000000001</v>
       </c>
-      <c r="T25" t="n">
-        <v>7.6364</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="T29" t="n">
+        <v>7.636400000000002</v>
+      </c>
+      <c r="U29" t="n">
         <v>0.9893999999999998</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>5.3163</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>7.646699999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-2.3305</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
